--- a/public/documents/pieces-reponse-1/R1-variation-de-stock-en-volumes.xlsx
+++ b/public/documents/pieces-reponse-1/R1-variation-de-stock-en-volumes.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>190,56</t>
+          <t>180,66</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>32,88</t>
+          <t>42,78</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>453,29</t>
+          <t>443,39</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>133,29</t>
+          <t>143,19</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>453,29</t>
+          <t>443,39</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>133,29</t>
+          <t>143,19</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>481,29</t>
+          <t>471,39</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>329,29</t>
+          <t>339,19</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>482,29</t>
+          <t>472,39</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>104,29</t>
+          <t>114,19</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I274"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1485,13 +1485,13 @@
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8,80</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Vittel 50cl</t>
+          <t>San Pellegrino 50cl</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>San Pellegrino 50cl</t>
+          <t>San Pellegrino 100cl</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>50,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>16,500</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>29,04</t>
+          <t>28,75</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>San Pellegrino 100cl</t>
+          <t>Orangina 33cl</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1711,27 +1711,27 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>10,890</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>28,75</t>
+          <t>19,47</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Orangina 33cl</t>
+          <t>Fanta 33cl</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>4,290</t>
+          <t>7,590</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>19,47</t>
+          <t>14,95</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Fanta 33cl</t>
+          <t>Schweppes 33cl</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>7,590</t>
+          <t>11,220</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>14,95</t>
+          <t>20,74</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Schweppes 33cl</t>
+          <t>Limonade Mortuacienne 1L</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1852,22 +1852,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>11,220</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>20,74</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Limonade Mortuacienne 1L</t>
+          <t>Granini Nectar Ananas</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1897,24 +1897,16 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>100,0</t>
-        </is>
-      </c>
+      <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>14,000</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>13,44</t>
+          <t>28,98</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1924,7 +1916,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>pas de contenance au libelle</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1928,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Granini Nectar Ananas</t>
+          <t>Granini Nectar Poire</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1947,13 +1939,13 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>28,98</t>
+          <t>27,28</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1975,7 +1967,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Granini Nectar Poire</t>
+          <t>Granini Jus Orange</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1986,13 +1978,13 @@
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27,28</t>
+          <t>18,78</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -2014,7 +2006,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Granini Jus Orange</t>
+          <t>Granini Jus Ananas</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2025,13 +2017,13 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>18,78</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2053,7 +2045,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Granini Jus Ananas</t>
+          <t>Granini Framboise 25cl</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2061,16 +2053,24 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>25,0</t>
+        </is>
+      </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>6,250</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>32,75</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>pas de contenance au libelle</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Granini Framboise 25cl</t>
+          <t>Granini Fraise 25cl</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>6,250</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>32,75</t>
+          <t>38,08</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Granini Fraise 25cl</t>
+          <t>Granini Raisin 25cl</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>4,750</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>38,08</t>
+          <t>20,33</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Granini Raisin 25cl</t>
+          <t>Granini Tomate 25cl</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>4,750</t>
+          <t>4,250</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>20,33</t>
+          <t>16,83</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Granini Tomate 25cl</t>
+          <t>Coca-Cola 33cl</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>25,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>4,250</t>
+          <t>30,360</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>16,83</t>
+          <t>58,88</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Coca-Cola 33cl</t>
+          <t>Fuze Tea 33cl</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2295,17 +2295,17 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>30,360</t>
+          <t>8,580</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>58,88</t>
+          <t>16,90</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Fuze Tea 33cl</t>
+          <t>Monin Pêche 100cl</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2337,22 +2337,22 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>8,580</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>16,90</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Monin Pêche 100cl</t>
+          <t>Monin Fraise 100cl</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Monin Fraise 100cl</t>
+          <t>Monin Châtaigne 100cl</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>5,31</t>
+          <t>16,50</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Monin Châtaigne 100cl</t>
+          <t>Monin Framboise 100cl</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2483,17 +2483,17 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>16,50</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Monin Framboise 100cl</t>
+          <t>Monin Citron 100cl</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Monin Citron 100cl</t>
+          <t>Monin Orange 100cl</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2577,17 +2577,17 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>9,10</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Monin Orange 100cl</t>
+          <t>Monin Grenadine 100cl</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2624,17 +2624,17 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>9,10</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Monin Grenadine 100cl</t>
+          <t>Monin Menthe 100cl</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Monin Menthe 100cl</t>
+          <t>Routin Citron Acide</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2711,24 +2711,16 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>100,0</t>
-        </is>
-      </c>
+      <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2738,7 +2730,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>pas de contenance au libelle</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2742,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Routin Citron Acide</t>
+          <t>Monin Pamplemousse 100cl</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2758,16 +2750,24 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>100,0</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>11,00</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>pas de contenance au libelle</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Monin Pamplemousse 100cl</t>
+          <t>Monin Curaçao 100cl</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>11,00</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2836,32 +2836,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Monin Curaçao 100cl</t>
+          <t>Rouget de Lisle Blanche 33cl</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>boisson_sans_alcool</t>
+          <t>alcool</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>13,530</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>73,80</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Blanche 33cl</t>
+          <t>Rouget de Lisle Ambrée 33cl</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2898,17 +2898,17 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>13,530</t>
+          <t>11,880</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>73,80</t>
+          <t>64,80</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Ambrée 33cl</t>
+          <t>Fût Affligem 8L</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2940,22 +2940,22 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>11,880</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>64,80</t>
+          <t>16,28</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>fut facture au litre : prix unitaire 4,07 EUR voisin du prix au litre, la quantite inventoriee est donc en litres</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Fût Affligem 8L</t>
+          <t>Cidre La Mordue 27cl</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2987,32 +2987,32 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>27,0</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>8,640</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>16,28</t>
+          <t>36,16</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>fut facture au litre : prix unitaire 4,07 EUR voisin du prix au litre, la quantite inventoriee est donc en litres</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Cidre La Mordue 27cl</t>
+          <t>Cidre Brut 75cl</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3034,27 +3034,27 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>27,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>8,640</t>
+          <t>11,250</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>36,16</t>
+          <t>38,10</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Cidre Brut 75cl</t>
+          <t>Cidre Doux 75cl</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>11,250</t>
+          <t>10,500</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>38,10</t>
+          <t>40,46</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Cidre Doux 75cl</t>
+          <t>Pontarlier Anis 100cl</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3128,22 +3128,22 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>40,46</t>
+          <t>17,95</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Pontarlier Anis 100cl</t>
+          <t>Ricard 100cl</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>17,56</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Ricard 100cl</t>
+          <t>Clan Campbell 70cl</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>17,56</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Clan Campbell 70cl</t>
+          <t>Jack Daniel's 70cl</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>17,56</t>
+          <t>19,26</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Jack Daniel's 70cl</t>
+          <t>Marc du Jura 70cl</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>18,61</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Marc du Jura 70cl</t>
+          <t>Martini 100cl</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>18,61</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Martini 100cl</t>
+          <t>Marc de Bourgogne 70cl</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Marc de Bourgogne 70cl</t>
+          <t>Porto 75cl</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30,84</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Porto 75cl</t>
+          <t>Liqueur de Sapin 100cl</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3504,22 +3504,22 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>30,84</t>
+          <t>42,32</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Liqueur de Sapin 100cl</t>
+          <t>Crème de Mûre 100cl</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>42,32</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Crème de Mûre 100cl</t>
+          <t>Crème de Cassis 100cl</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3603,17 +3603,17 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>16,78</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Crème de Cassis 100cl</t>
+          <t>Crème de Cerise 100cl</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>16,78</t>
+          <t>15,76</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Crème de Cerise 100cl</t>
+          <t>Vodka Poliakov 70cl</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3692,22 +3692,22 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>16,78</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Vodka Poliakov 70cl</t>
+          <t>Cognac Park 70cl</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>9,03</t>
+          <t>19,62</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Cognac Park 70cl</t>
+          <t>Absinthe 70cl</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>19,62</t>
+          <t>61,78</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Absinthe 70cl</t>
+          <t>Calvados 100cl</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>61,78</t>
+          <t>33,06</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Calvados 100cl</t>
+          <t>Mirabelle 70cl</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3880,22 +3880,22 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>33,06</t>
+          <t>20,04</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Mirabelle 70cl</t>
+          <t>Eau de Vie Framboise 70cl</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>20,04</t>
+          <t>21,65</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Eau de Vie Framboise 70cl</t>
+          <t>Soho Litchi 70cl</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3979,17 +3979,17 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>21,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Soho Litchi 70cl</t>
+          <t>Passoa 70cl</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4026,17 +4026,17 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18,16</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Passoa 70cl</t>
+          <t>Bailey's 70cl</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4073,17 +4073,17 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>18,16</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Bailey's 70cl</t>
+          <t>Picon 100cl</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -4115,22 +4115,22 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10,43</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Picon 100cl</t>
+          <t>Get 27 70cl</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>10,43</t>
+          <t>15,36</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Get 27 70cl</t>
+          <t>Get 31 70cl</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>15,36</t>
+          <t>17,26</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Get 31 70cl</t>
+          <t>Génépi 70cl</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>17,26</t>
+          <t>22,66</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Génépi 70cl</t>
+          <t>Ravelin Blanc 99cl</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4303,22 +4303,22 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>99,0</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>22,66</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Ravelin Blanc 99cl</t>
+          <t>Chardonnay Tradition 75cl</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>99,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Chardonnay Tradition 75cl</t>
+          <t>Bourgogne Aligoté BIB 10L</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>1 000,0</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>51,24</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Bourgogne Aligoté BIB 10L</t>
+          <t>BIB Côtes de Provence Rosé 10L</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4449,17 +4449,17 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>51,24</t>
+          <t>105,50</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>BIB Côtes de Provence Rosé 10L</t>
+          <t>BIB Côtes du Rhône Rouge 10L</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>105,50</t>
+          <t>31,30</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>BIB Côtes du Rhône Rouge 10L</t>
+          <t>Ravelin 75cl</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -4538,22 +4538,22 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1 000,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>31,30</t>
+          <t>26,73</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Ravelin 75cl</t>
+          <t>Gewurztraminer 75cl</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -4590,17 +4590,17 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>6,750</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>26,73</t>
+          <t>99,70</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Gewurztraminer 75cl</t>
+          <t>Saint Joseph Rouge 75cl</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -4637,17 +4637,17 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>99,70</t>
+          <t>116,64</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge 75cl</t>
+          <t>Moulin à Vent 75cl</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -4684,17 +4684,17 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>6,750</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>116,64</t>
+          <t>87,04</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Moulin à Vent 75cl</t>
+          <t>Haute Côte de Beaune 75cl</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>87,04</t>
+          <t>85,44</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Haute Côte de Beaune 75cl</t>
+          <t>Chablis 75cl</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>5,250</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>85,44</t>
+          <t>93,59</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Chablis 75cl</t>
+          <t>Saint Véran 75cl</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -4825,17 +4825,17 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>5,250</t>
+          <t>18,750</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>93,59</t>
+          <t>436,50</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Saint Véran 75cl</t>
+          <t>Bordeaux Supérieur 75cl</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4872,17 +4872,17 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>18,750</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>436,50</t>
+          <t>6,28</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Bordeaux Supérieur 75cl</t>
+          <t>Grand Pavois 75cl</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4919,17 +4919,17 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>0,750</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Grand Pavois 75cl</t>
+          <t>Arbois Trousseau 75cl</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4966,17 +4966,17 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>97,70</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Arbois Trousseau 75cl</t>
+          <t>Arbois Béthanie 75cl</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5013,17 +5013,17 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>10,500</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>97,70</t>
+          <t>144,34</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Arbois Béthanie 75cl</t>
+          <t>Vin de Paille 37,5cl</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -5055,22 +5055,22 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>144,34</t>
+          <t>33,22</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Vin de Paille 37,5cl</t>
+          <t>Arbois Savagnin 75cl</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5102,22 +5102,22 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>0,750</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>33,22</t>
+          <t>94,80</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Arbois Savagnin 75cl</t>
+          <t>Arbois Béthanie 37,5cl</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>94,80</t>
+          <t>106,88</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Arbois Béthanie 37,5cl</t>
+          <t>Arbois Chardonnay 75cl</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>13,500</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>106,88</t>
+          <t>130,86</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Arbois Chardonnay 75cl</t>
+          <t>Arbois Vin Jaune 62cl</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -5243,22 +5243,22 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>62,0</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>2,480</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>130,86</t>
+          <t>76,52</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Arbois Vin Jaune 62cl</t>
+          <t>L'Esprit Grassier Rosé 75cl</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5290,22 +5290,22 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>62,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>2,480</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>76,52</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>L'Esprit Grassier Rosé 75cl</t>
+          <t>Bohème Rosé (Le Pive) 75cl</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>82,80</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Bohème Rosé (Le Pive) 75cl</t>
+          <t>Rosé Les Jamelles 75cl</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5389,17 +5389,17 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>82,80</t>
+          <t>39,92</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles 75cl</t>
+          <t>Champagne Ruinart 75cl</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>39,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Champagne Ruinart 75cl</t>
+          <t>Champagne Jean Sandrin 75cl</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -5483,17 +5483,17 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132,40</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Champagne Jean Sandrin 75cl</t>
+          <t>Crémant du Jura 75cl</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>132,40</t>
+          <t>62,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Crémant du Jura 75cl</t>
+          <t>Macvin 75cl</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,750</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>62,00</t>
+          <t>68,35</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Macvin 75cl</t>
+          <t>Grand Marnier 70cl</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -5619,22 +5619,22 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>3,750</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>68,35</t>
+          <t>42,16</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Grand Marnier 70cl</t>
+          <t>Crème de Cassis 70cl</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>42,16</t>
+          <t>17,42</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Crème de Cassis 70cl</t>
+          <t>Liqueur de Poire 70cl</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5718,17 +5718,17 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>17,42</t>
+          <t>16,43</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Liqueur de Poire 70cl</t>
+          <t>Liqueur de Sapin 70cl</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>16,43</t>
+          <t>37,82</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -5792,37 +5792,29 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2023-03-31</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Liqueur de Sapin 70cl</t>
+          <t>Malongo Grain Kilo Select</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>alcool</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>70,0</t>
-        </is>
-      </c>
+          <t>boisson_sans_alcool</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr"/>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>1,400</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>37,82</t>
+          <t>29,92</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -5832,7 +5824,7 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>pas de contenance au libelle</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5836,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Malongo Grain Kilo Select</t>
+          <t>Malongo Déca Moulu Aqua 250g</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5861,7 +5853,7 @@
       <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>29,92</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -5883,7 +5875,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Malongo Déca Moulu Aqua 250g</t>
+          <t>Thé Vert Menthe x25 sachets</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -5900,7 +5892,7 @@
       <c r="F104" s="4" t="inlineStr"/>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -5922,7 +5914,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Thé Vert Menthe x25 sachets</t>
+          <t>Verveine Menthe x25 sachets</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -5939,7 +5931,7 @@
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5961,7 +5953,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Verveine Menthe x25 sachets</t>
+          <t>Earl Grey x25 sachets</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -5978,7 +5970,7 @@
       <c r="F106" s="4" t="inlineStr"/>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -6000,7 +5992,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Earl Grey x25 sachets</t>
+          <t>Thé Fruits Rouges x25 sachets</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -6039,7 +6031,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Thé Fruits Rouges x25 sachets</t>
+          <t>Infusion Segafredo 20 sachets</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -6056,7 +6048,7 @@
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -6078,7 +6070,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Infusion Segafredo 20 sachets</t>
+          <t>Vittel 100cl</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -6086,16 +6078,24 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr"/>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>100,0</t>
+        </is>
+      </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>21,50</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>pas de contenance au libelle</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Vittel 100cl</t>
+          <t>Vittel 50cl</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>50,0</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>12,500</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>21,50</t>
+          <t>17,50</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Vittel 50cl</t>
+          <t>La Bleue (eau) 50cl</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -6179,22 +6179,22 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>17,50</t>
+          <t>11,28</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
@@ -6211,32 +6211,32 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>La Bleue (eau) 50cl</t>
+          <t>Rouget de Lisle Blanche 33cl</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>boisson_sans_alcool</t>
+          <t>alcool</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>50,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>6,270</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>34,80</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Blanche 33cl</t>
+          <t>Rouget de Lisle Ambrée 33cl</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>6,270</t>
+          <t>7,260</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>34,80</t>
+          <t>41,14</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Ambrée 33cl</t>
+          <t>Fût Affligem Blade 8L 6,7°</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -6315,32 +6315,32 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>7,260</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>41,14</t>
+          <t>135,36</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>fut facture au litre : prix unitaire 4,23 EUR voisin du prix au litre, la quantite inventoriee est donc en litres</t>
         </is>
       </c>
     </row>
@@ -6352,42 +6352,42 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Fût Affligem Blade 8L 6,7°</t>
+          <t>Orangina 33cl</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>alcool</t>
+          <t>boisson_sans_alcool</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>16,500</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>135,36</t>
+          <t>30,50</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>fut facture au litre : prix unitaire 4,23 EUR voisin du prix au litre, la quantite inventoriee est donc en litres</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Orangina 33cl</t>
+          <t>Fanta Citron Frappé 33cl</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -6414,17 +6414,17 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>16,500</t>
+          <t>8,580</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>30,50</t>
+          <t>18,98</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Fanta Citron Frappé 33cl</t>
+          <t>Schweppes Agrum 33cl</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -6461,17 +6461,17 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>8,580</t>
+          <t>17,160</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>18,98</t>
+          <t>33,28</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Schweppes Agrum 33cl</t>
+          <t>Limonade Mortuacienne 1L</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>17,160</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>33,28</t>
+          <t>14,40</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Limonade Mortuacienne 1L</t>
+          <t>Granini Jus Pomme 1L</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -6555,22 +6555,22 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>14,40</t>
+          <t>16,80</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Granini Jus Pomme 1L</t>
+          <t>Granini Jus Orange 1L</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -6602,22 +6602,22 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>16,80</t>
+          <t>16,90</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Granini Jus Orange 1L</t>
+          <t>Granini Jus Ananas 1L</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -6649,17 +6649,17 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>16,90</t>
+          <t>33,90</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Granini Jus Ananas 1L</t>
+          <t>Norbert Jus Orange sans pulpe 1L</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -6696,17 +6696,17 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>33,90</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Norbert Jus Orange sans pulpe 1L</t>
+          <t>Granini Fraise 25cl</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -6738,22 +6738,22 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>25,0</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>58,56</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Granini Fraise 25cl</t>
+          <t>Granini Jus de Tomate 25cl</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -6790,22 +6790,22 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>5,750</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>58,56</t>
+          <t>28,06</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Granini Jus de Tomate 25cl</t>
+          <t>Coca-Cola 33cl</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -6832,22 +6832,22 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>25,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>5,750</t>
+          <t>38,280</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>28,06</t>
+          <t>71,92</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Coca-Cola 33cl</t>
+          <t>Fuzetea Pêche 33cl</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>38,280</t>
+          <t>12,870</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>71,92</t>
+          <t>28,47</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Fuzetea Pêche 33cl</t>
+          <t>Pulco Citron 70cl</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -6926,22 +6926,22 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>12,870</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>28,47</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Pulco Citron 70cl</t>
+          <t>Monin Pêche 100cl</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -6973,22 +6973,22 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>12,22</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Monin Pêche 100cl</t>
+          <t>Monin Cerise 100cl</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -7025,17 +7025,17 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>12,22</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Monin Cerise 100cl</t>
+          <t>Monin Menthe Verte 100cl</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Monin Menthe Verte 100cl</t>
+          <t>Monin Châtaigne 100cl</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -7119,17 +7119,17 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>8,64</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Monin Châtaigne 100cl</t>
+          <t>Monin Framboise 100cl</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>19,08</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Monin Framboise 100cl</t>
+          <t>Jus de Poire 100cl</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -7213,17 +7213,17 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>19,08</t>
+          <t>53,30</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Jus de Poire 100cl</t>
+          <t>Monin Pamplemousse Rose 70cl</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -7255,22 +7255,22 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>53,30</t>
+          <t>16,83</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -7292,32 +7292,32 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Monin Pamplemousse Rose 70cl</t>
+          <t>Cidre La Mordue Original 27cl</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>boisson_sans_alcool</t>
+          <t>alcool</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>27,0</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>5,130</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>16,83</t>
+          <t>22,23</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Cidre La Mordue Original 27cl</t>
+          <t>Cidre Brut Bolée d'Armorique 75cl</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -7349,22 +7349,22 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>27,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>5,130</t>
+          <t>11,250</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>22,23</t>
+          <t>41,25</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Cidre Brut Bolée d'Armorique 75cl</t>
+          <t>Cidre Doux Contemporaine 75cl</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>11,250</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>41,25</t>
+          <t>46,24</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Cidre Doux Contemporaine 75cl</t>
+          <t>Pontarlier Anis Sec 100cl 45°</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -7443,22 +7443,22 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>46,24</t>
+          <t>37,70</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Pontarlier Anis Sec 100cl 45°</t>
+          <t>Ricard 100cl 45°</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -7495,17 +7495,17 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>37,70</t>
+          <t>17,95</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Ricard 100cl 45°</t>
+          <t>Pastis 51 100cl 45°</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>16,44</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Pastis 51 100cl 45°</t>
+          <t>Macvin Blanc 75cl 18° (Rolet)</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -7584,22 +7584,22 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>16,44</t>
+          <t>140,67</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Macvin Blanc 75cl 18° (Rolet)</t>
+          <t>Macvin du Jura Rosé 75cl (Arbois)</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -7636,17 +7636,17 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>6,750</t>
+          <t>0,000</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>140,67</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Macvin du Jura Rosé 75cl (Arbois)</t>
+          <t>Marc du Jura Tissot 70cl</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -7678,22 +7678,22 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>0,000</t>
+          <t>2,100</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>58,44</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Marc du Jura Tissot 70cl</t>
+          <t>Martini Bianco 100cl 14,4°</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -7725,22 +7725,22 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>58,44</t>
+          <t>16,34</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Martini Bianco 100cl 14,4°</t>
+          <t>Porto Sandeman Rouge 75cl 19,5°</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -7772,22 +7772,22 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>16,34</t>
+          <t>32,12</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Porto Sandeman Rouge 75cl 19,5°</t>
+          <t>Vert Sapin 40° 100cl</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -7819,22 +7819,22 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>32,12</t>
+          <t>21,36</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Vert Sapin 40° 100cl</t>
+          <t>Grand Marnier Cordon Rouge 70cl 40°</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>21,36</t>
+          <t>21,79</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Grand Marnier Cordon Rouge 70cl 40°</t>
+          <t>Crème Cassis 15° 100cl Massenez</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -7913,22 +7913,22 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>21,79</t>
+          <t>27,00</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Crème Cassis 15° 100cl Massenez</t>
+          <t>Crème Mûre 15° 100cl Massenez</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>27,00</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Crème Mûre 15° 100cl Massenez</t>
+          <t>Liqueur Golden Eight Poire William 70cl 25°</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -8017,12 +8017,12 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>18,54</t>
+          <t>34,22</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Liqueur Golden Eight Poire William 70cl 25°</t>
+          <t>Crème Cassis Briottet 20° 70cl</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>34,22</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Crème Cassis Briottet 20° 70cl</t>
+          <t>Calvados Beaujour 100cl 40°</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -8101,22 +8101,22 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>9,03</t>
+          <t>33,54</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Calvados Beaujour 100cl 40°</t>
+          <t>Mirabelle Grande Réserve 1811 70cl 42°</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -8148,22 +8148,22 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>33,54</t>
+          <t>20,65</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Mirabelle Grande Réserve 1811 70cl 42°</t>
+          <t>Framboise Sauvage 70cl 40° (Massenez)</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -8200,17 +8200,17 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>20,65</t>
+          <t>45,76</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Framboise Sauvage 70cl 40° (Massenez)</t>
+          <t>Aperol 100cl 12,5°</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>45,76</t>
+          <t>29,32</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Aperol 100cl 12,5°</t>
+          <t>Soho Litchi 70cl 15°</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -8289,22 +8289,22 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>29,32</t>
+          <t>10,44</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Soho Litchi 70cl 15°</t>
+          <t>Passoa 70cl 15°</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -8341,22 +8341,22 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>10,44</t>
+          <t>19,78</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Passoa 70cl 15°</t>
+          <t>Bailey's 70cl 17°</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -8388,22 +8388,22 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>19,78</t>
+          <t>13,46</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Bailey's 70cl 17°</t>
+          <t>Get 27 Vert 100cl 17,9°</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -8440,17 +8440,17 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>13,46</t>
+          <t>15,36</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Get 27 Vert 100cl 17,9°</t>
+          <t>Get 31 100cl 24°</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>15,36</t>
+          <t>17,26</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Get 31 100cl 24°</t>
+          <t>Génépi 40° 70cl</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>17,26</t>
+          <t>23,51</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Génépi 40° 70cl</t>
+          <t>Ravelin Blanc MVPCE 13° 99cl (A.Bonnot)</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -8571,22 +8571,22 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>99,0</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>11,880</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>23,51</t>
+          <t>39,48</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Ravelin Blanc MVPCE 13° 99cl (A.Bonnot)</t>
+          <t>Ravelin Blanc BIB 10L 13° (A.Bonnot)</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -8618,22 +8618,22 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>99,0</t>
+          <t>1 000,0</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>11,880</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>39,48</t>
+          <t>27,40</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Ravelin Blanc BIB 10L 13° (A.Bonnot)</t>
+          <t>Bourgogne Aligoté BIB 10L</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>27,40</t>
+          <t>162,87</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Bourgogne Aligoté BIB 10L</t>
+          <t>Côtes de Provence Rosé BIB 10L</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>162,87</t>
+          <t>158,25</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Côtes de Provence Rosé BIB 10L</t>
+          <t>Côtes du Rhône Rouge BIB 10L</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -8764,17 +8764,17 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>158,25</t>
+          <t>30,38</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Côtes du Rhône Rouge BIB 10L</t>
+          <t>Gewurztraminer Les Sorcières 75cl 2018</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -8806,22 +8806,22 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>1 000,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>8,250</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>30,38</t>
+          <t>109,67</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Gewurztraminer Les Sorcières 75cl 2018</t>
+          <t>Saint Joseph Rouge 75cl 2022 (Ogier)</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -8858,17 +8858,17 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>8,250</t>
+          <t>2,250</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>109,67</t>
+          <t>41,40</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge 75cl 2022 (Ogier)</t>
+          <t>Moulin à Vent 75cl 2017 (Briante)</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -8905,17 +8905,17 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>2,250</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>41,40</t>
+          <t>97,92</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Moulin à Vent 75cl 2017 (Briante)</t>
+          <t>Macon Roche Blanche 75cl 2021</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -8952,17 +8952,17 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>6,750</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>97,92</t>
+          <t>139,68</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Macon Roche Blanche 75cl 2021</t>
+          <t>Chablis Saint Martin 75cl 2022 (Laroche)</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -8999,17 +8999,17 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>9,750</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>139,68</t>
+          <t>168,61</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Chablis Saint Martin 75cl 2022 (Laroche)</t>
+          <t>Petit Chablis 75cl 2021 (Louis Moreau)</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>9,750</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>168,61</t>
+          <t>11,01</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Petit Chablis 75cl 2021 (Louis Moreau)</t>
+          <t>Saint Véran 75cl 2020 (Lupé Cholet)</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -9093,17 +9093,17 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>0,750</t>
+          <t>8,250</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>187,33</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Saint Véran 75cl 2020 (Lupé Cholet)</t>
+          <t>Sauternes 75cl 2015 (Suduiraut)</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -9140,17 +9140,17 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>8,250</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>187,33</t>
+          <t>12,81</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Sauternes 75cl 2015 (Suduiraut)</t>
+          <t>Grand Pavois N°8 Blanc 75cl</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -9187,17 +9187,17 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>0,750</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>12,81</t>
+          <t>41,84</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Grand Pavois N°8 Blanc 75cl</t>
+          <t>Arbois Trousseau 75cl 2022 (J-L Tissot)</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>5,250</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>41,84</t>
+          <t>75,11</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Arbois Trousseau 75cl 2022 (J-L Tissot)</t>
+          <t>Arbois Blanc Cuvée Béthanie 75cl 2018</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -9281,17 +9281,17 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>5,250</t>
+          <t>11,250</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>75,11</t>
+          <t>163,20</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Arbois Blanc Cuvée Béthanie 75cl 2018</t>
+          <t>Vin de Paille 37,5cl 2017</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -9323,22 +9323,22 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>11,250</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>163,20</t>
+          <t>66,44</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Vin de Paille 37,5cl 2017</t>
+          <t>Arbois Savagnin 75cl 2018</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -9370,22 +9370,22 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>66,44</t>
+          <t>94,80</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Arbois Savagnin 75cl 2018</t>
+          <t>Arbois Blanc Cuvée Béthanie 37,5cl</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -9417,22 +9417,22 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>94,80</t>
+          <t>134,40</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Arbois Blanc Cuvée Béthanie 37,5cl</t>
+          <t>Arbois Chardonnay 75cl 2020 (J-L Tissot)</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>134,40</t>
+          <t>159,20</t>
         </is>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Arbois Chardonnay 75cl 2020 (J-L Tissot)</t>
+          <t>Arbois Vin Jaune 62cl 2016 (J-L Tissot)</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -9511,22 +9511,22 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>62,0</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>1,240</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>159,20</t>
+          <t>59,40</t>
         </is>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Arbois Vin Jaune 62cl 2016 (J-L Tissot)</t>
+          <t>Arbois Vin Jaune 62cl 2017 (J-L Tissot)</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -9563,22 +9563,22 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>1,240</t>
+          <t>1,860</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>59,40</t>
+          <t>89,10</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Arbois Vin Jaune 62cl 2017 (J-L Tissot)</t>
+          <t>Rosé Le Pive 2022 75cl</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>62,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>1,860</t>
+          <t>2,250</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>89,10</t>
+          <t>19,05</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Rosé Le Pive 2022 75cl</t>
+          <t>Rosé Les Jamelles 75cl 2022</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -9657,17 +9657,17 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>2,250</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>19,05</t>
+          <t>83,36</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles 75cl 2022</t>
+          <t>Côtes de Provence Rosé Minuty 75cl 2022</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -9704,17 +9704,17 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>83,36</t>
+          <t>158,52</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Côtes de Provence Rosé Minuty 75cl 2022</t>
+          <t>La Côte Rouge 75cl 2021 (La Clape)</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -9751,17 +9751,17 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>3,750</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>158,52</t>
+          <t>40,30</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>La Côte Rouge 75cl 2021 (La Clape)</t>
+          <t>Champagne Ruinart 75cl</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -9798,17 +9798,17 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>3,750</t>
+          <t>0,750</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>40,30</t>
+          <t>44,63</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Champagne Ruinart 75cl</t>
+          <t>Champagne Lanson Black Label 75cl</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -9845,17 +9845,17 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>0,750</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>44,63</t>
+          <t>194,80</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Champagne Lanson Black Label 75cl</t>
+          <t>Champagne Jean Sandrin Brut 75cl</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -9892,17 +9892,17 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>194,80</t>
+          <t>148,95</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Champagne Jean Sandrin Brut 75cl</t>
+          <t>Crémant du Jura Blanc 75cl (Arbois)</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -9939,22 +9939,22 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>6,750</t>
+          <t>14,250</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>148,95</t>
+          <t>171,19</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -9966,12 +9966,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Crémant du Jura Blanc 75cl (Arbois)</t>
+          <t>Rosé Le Pive 75cl</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -9986,22 +9986,22 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>14,250</t>
+          <t>10,500</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>171,19</t>
+          <t>88,90</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Rosé Le Pive 75cl</t>
+          <t>Génépi 70cl</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -10028,22 +10028,22 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>88,90</t>
+          <t>23,53</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Génépi 70cl</t>
+          <t>Get 27 70cl</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>23,53</t>
+          <t>15,36</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Get 27 70cl</t>
+          <t>Get 31 70cl</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>15,36</t>
+          <t>17,26</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Get 31 70cl</t>
+          <t>Crème de Cassis 100cl</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -10169,22 +10169,22 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>17,26</t>
+          <t>27,00</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Crème de Cassis 100cl</t>
+          <t>Cognac 70cl</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -10216,22 +10216,22 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>27,00</t>
+          <t>41,64</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Cognac 70cl</t>
+          <t>Calvados 100cl</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -10263,22 +10263,22 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>41,64</t>
+          <t>16,77</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Calvados 100cl</t>
+          <t>Jack Daniel's 70cl</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>16,77</t>
+          <t>19,26</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Jack Daniel's 70cl</t>
+          <t>Clan Campbell 70cl</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>12,80</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Clan Campbell 70cl</t>
+          <t>Vodka 70cl</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>12,80</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Vodka 70cl</t>
+          <t>Liqueur de Sapin 100cl</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
-          <t>9,67</t>
+          <t>21,36</t>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Liqueur de Sapin 100cl</t>
+          <t>Eau de Vie de Poire 70cl</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>21,36</t>
+          <t>22,88</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Eau de Vie de Poire 70cl</t>
+          <t>Marc de Bourgogne 70cl</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t>22,88</t>
+          <t>25,90</t>
         </is>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Marc de Bourgogne 70cl</t>
+          <t>Liqueur de Cerise 70cl</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -10597,17 +10597,17 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>25,90</t>
+          <t>18,06</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Liqueur de Cerise 70cl</t>
+          <t>Grand Marnier 70cl</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
-          <t>18,06</t>
+          <t>21,79</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Grand Marnier 70cl</t>
+          <t>Ricard 100cl</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
         <is>
-          <t>21,79</t>
+          <t>17,95</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Ricard 100cl</t>
+          <t>Pastis 51 100cl</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>16,44</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Pastis 51 100cl</t>
+          <t>Absinthe 70cl</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -10780,22 +10780,22 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>16,44</t>
+          <t>48,02</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Absinthe 70cl</t>
+          <t>Vin de Paille 37,5cl</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -10827,22 +10827,22 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>1,125</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>48,02</t>
+          <t>49,83</t>
         </is>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Vin de Paille 37,5cl</t>
+          <t>Eau de Vie Framboise 70cl</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -10874,22 +10874,22 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>1,125</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
-          <t>49,83</t>
+          <t>22,88</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Eau de Vie Framboise 70cl</t>
+          <t>Eau de Vie Mirabelle 70cl</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>22,88</t>
+          <t>20,69</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Eau de Vie Mirabelle 70cl</t>
+          <t>Arbois Blanc Cuvée Béthanie 75cl</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -10968,22 +10968,22 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>12,750</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>184,96</t>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Arbois Blanc Cuvée Béthanie 75cl</t>
+          <t>Arbois Chardonnay 75cl</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -11020,22 +11020,22 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>12,750</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>184,96</t>
+          <t>129,36</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Arbois Chardonnay 75cl</t>
+          <t>Saint Véran 75cl</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -11067,22 +11067,22 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>5,250</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>129,36</t>
+          <t>119,21</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Saint Véran 75cl</t>
+          <t>Macon 75cl</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -11114,22 +11114,22 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>5,250</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>119,21</t>
+          <t>48,41</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Macon 75cl</t>
+          <t>Chablis 75cl</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -11161,22 +11161,22 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>48,41</t>
+          <t>207,52</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Chablis 75cl</t>
+          <t>Crémant du Jura 75cl</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -11208,17 +11208,17 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>207,52</t>
+          <t>81,09</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Crémant du Jura 75cl</t>
+          <t>Cidre Brut 75cl</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -11255,17 +11255,17 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>6,750</t>
+          <t>16,500</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>81,09</t>
+          <t>60,50</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Cidre Brut 75cl</t>
+          <t>Rouget de Lisle Blanche 33cl</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
@@ -11297,22 +11297,22 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>16,500</t>
+          <t>2,970</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>60,50</t>
+          <t>16,20</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Blanche 33cl</t>
+          <t>Rouget de Lisle Ambrée 33cl</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -11349,17 +11349,17 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>2,970</t>
+          <t>8,910</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>16,20</t>
+          <t>50,49</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Rouget de Lisle Ambrée 33cl</t>
+          <t>Cidre La Mordue 27cl</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>27,0</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>8,910</t>
+          <t>4,860</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>50,49</t>
+          <t>21,06</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Cidre La Mordue 27cl</t>
+          <t>Gewurztraminer 75cl</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -11438,22 +11438,22 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>27,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>4,860</t>
+          <t>2,250</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>21,06</t>
+          <t>29,91</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Gewurztraminer 75cl</t>
+          <t>Côtes de Gascogne 75cl</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
@@ -11490,17 +11490,17 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>2,250</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>29,91</t>
+          <t>20,92</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Côtes de Gascogne 75cl</t>
+          <t>BIB Rosé 10L</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -11532,22 +11532,22 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>1 000,0</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>20,92</t>
+          <t>158,25</t>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>BIB Rosé 10L</t>
+          <t>BIB Rouge 10L</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>158,25</t>
+          <t>30,38</t>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>BIB Rouge 10L</t>
+          <t>BIB Blanc 10L</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -11631,17 +11631,17 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>30,38</t>
+          <t>108,58</t>
         </is>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>BIB Blanc 10L</t>
+          <t>Fût Affligem 8L</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
@@ -11673,22 +11673,22 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>1 000,0</t>
+          <t>800,0</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>108,58</t>
+          <t>169,20</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>fut compte a l'unite : prix unitaire 33,84 EUR voisin de 8 fois le prix au litre</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Fût Affligem 8L</t>
+          <t>[Page 9 - écart ~92 € : 1 ligne vin non identifiée]</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -11718,34 +11718,26 @@
           <t>alcool</t>
         </is>
       </c>
-      <c r="D229" s="4" t="inlineStr">
-        <is>
-          <t>800,0</t>
-        </is>
-      </c>
+      <c r="D229" s="4" t="inlineStr"/>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F229" s="4" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr"/>
       <c r="G229" s="4" t="inlineStr">
         <is>
-          <t>169,20</t>
+          <t>91,97</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>fut compte a l'unite : prix unitaire 33,84 EUR voisin de 8 fois le prix au litre</t>
+          <t>pas de contenance au libelle</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11749,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>[Page 9 - écart ~92 € : 1 ligne vin non identifiée]</t>
+          <t>Passoa 70cl</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -11765,16 +11757,24 @@
           <t>alcool</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr"/>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>70,0</t>
+        </is>
+      </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F230" s="4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>1,400</t>
+        </is>
+      </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>91,97</t>
+          <t>19,67</t>
         </is>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>pas de contenance au libelle</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -11796,7 +11796,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Passoa 70cl</t>
+          <t>Soho Litchi 70cl</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -11811,22 +11811,22 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>19,67</t>
+          <t>10,44</t>
         </is>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Soho Litchi 70cl</t>
+          <t>Grand Marnier 70cl</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>10,44</t>
+          <t>21,79</t>
         </is>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Grand Marnier 70cl</t>
+          <t>Martini Blanc 100cl</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -11910,12 +11910,12 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
-          <t>21,79</t>
+          <t>8,17</t>
         </is>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Martini Blanc 100cl</t>
+          <t>Vin de Paille 37,5cl</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
@@ -11947,22 +11947,22 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,875</t>
         </is>
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>8,17</t>
+          <t>83,05</t>
         </is>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Vin de Paille 37,5cl</t>
+          <t>Bailey's 70cl</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -11994,22 +11994,22 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>1,875</t>
+          <t>0,700</t>
         </is>
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>83,05</t>
+          <t>13,46</t>
         </is>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Bailey's 70cl</t>
+          <t>Aperol 100cl</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
@@ -12041,22 +12041,22 @@
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
-          <t>0,700</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>13,46</t>
+          <t>29,32</t>
         </is>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Aperol 100cl</t>
+          <t>Liqueur de Poire William 70cl</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>29,32</t>
+          <t>34,22</t>
         </is>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Liqueur de Poire William 70cl</t>
+          <t>Champagne Jean Sandrin 75cl</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
@@ -12135,27 +12135,27 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>9,750</t>
         </is>
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>34,22</t>
+          <t>316,55</t>
         </is>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Champagne Jean Sandrin 75cl</t>
+          <t>Porto 75cl</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -12187,22 +12187,22 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>9,750</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
-          <t>316,55</t>
+          <t>16,06</t>
         </is>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Porto 75cl</t>
+          <t>Arbois Vin Jaune 62cl</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>62,0</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F240" s="4" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>1,240</t>
         </is>
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>16,06</t>
+          <t>59,40</t>
         </is>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Arbois Vin Jaune 62cl</t>
+          <t>Arbois Trousseau 75cl</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -12276,22 +12276,22 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>62,0</t>
+          <t>75,0</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>1,240</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>59,40</t>
+          <t>85,84</t>
         </is>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Arbois Trousseau 75cl</t>
+          <t>Hautes Côtes de Beaune 75cl</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
@@ -12338,12 +12338,12 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>85,84</t>
+          <t>115,41</t>
         </is>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune 75cl</t>
+          <t>Saint Joseph Rouge 75cl</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -12375,22 +12375,22 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>6,750</t>
         </is>
       </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
-          <t>115,41</t>
+          <t>124,20</t>
         </is>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge 75cl</t>
+          <t>Arbois Savagnin 75cl</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
@@ -12422,17 +12422,17 @@
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>6,750</t>
+          <t>9,750</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>124,20</t>
+          <t>154,05</t>
         </is>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Arbois Savagnin 75cl</t>
+          <t>Moulin à Vent 75cl</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>9,750</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>154,05</t>
+          <t>118,20</t>
         </is>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Moulin à Vent 75cl</t>
+          <t>Côtes de Provence Rosé Minuty 75cl</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
@@ -12516,17 +12516,17 @@
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>3,750</t>
         </is>
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>118,20</t>
+          <t>66,05</t>
         </is>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Côtes de Provence Rosé Minuty 75cl</t>
+          <t>Rosé Les Jamelles 75cl</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -12563,17 +12563,17 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>3,750</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>66,05</t>
+          <t>83,36</t>
         </is>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles 75cl</t>
+          <t>Arbois Blanc Cuvée Béthanie 37,5cl</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
@@ -12605,22 +12605,22 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>75,0</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>5,625</t>
         </is>
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>83,36</t>
+          <t>100,80</t>
         </is>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Arbois Blanc Cuvée Béthanie 37,5cl</t>
+          <t>[Page 10 - écart a fiabiliser]</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -12650,34 +12650,26 @@
           <t>alcool</t>
         </is>
       </c>
-      <c r="D249" s="4" t="inlineStr">
-        <is>
-          <t>37,5</t>
-        </is>
-      </c>
+      <c r="D249" s="4" t="inlineStr"/>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F249" s="4" t="inlineStr">
-        <is>
-          <t>5,625</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr"/>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>100,80</t>
+          <t>226,44</t>
         </is>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>pas de contenance au libelle</t>
         </is>
       </c>
     </row>
@@ -12689,24 +12681,32 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>[Page 10 - écart a fiabiliser]</t>
+          <t>Jus de Poire 1L</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>alcool</t>
-        </is>
-      </c>
-      <c r="D250" s="4" t="inlineStr"/>
+          <t>boisson_sans_alcool</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>100,0</t>
+        </is>
+      </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F250" s="4" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>226,44</t>
+          <t>30,70</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="I250" s="3" t="inlineStr">
         <is>
-          <t>pas de contenance au libelle</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Jus de Poire 1L</t>
+          <t>Jus Ananas 1L</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
@@ -12743,22 +12743,22 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>30,70</t>
+          <t>27,12</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Jus Ananas 1L</t>
+          <t>Jus Pomme 1L</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
@@ -12790,17 +12790,17 @@
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>27,12</t>
+          <t>50,40</t>
         </is>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Jus Pomme 1L</t>
+          <t>Jus Orange 1L</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -12837,17 +12837,17 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>50,40</t>
+          <t>30,42</t>
         </is>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Jus Orange 1L</t>
+          <t>Sirop Pulco/divers 70cl</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -12879,27 +12879,27 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>70,0</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>30,42</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Sirop Pulco/divers 70cl</t>
+          <t>Sirop Châtaigne 100cl</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>70,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>9,68</t>
+          <t>11,22</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Sirop Châtaigne 100cl</t>
+          <t>Sirop Orange 100cl</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>11,22</t>
+          <t>9,28</t>
         </is>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Sirop Orange 100cl</t>
+          <t>Sirop Cerise 100cl</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Sirop Cerise 100cl</t>
+          <t>Coca-Cola 33cl</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
@@ -13067,27 +13067,27 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>38,940</t>
         </is>
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>12,72</t>
+          <t>77,88</t>
         </is>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>a_verifier</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>Coca-Cola 33cl</t>
+          <t>Fuzetea 33cl</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -13119,17 +13119,17 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>38,940</t>
+          <t>18,810</t>
         </is>
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>77,88</t>
+          <t>41,61</t>
         </is>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Fuzetea 33cl</t>
+          <t>Schweppes Agrum 33cl</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
@@ -13166,17 +13166,17 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>18,810</t>
+          <t>8,910</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>41,61</t>
+          <t>19,80</t>
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Schweppes Agrum 33cl</t>
+          <t>Fanta 33cl</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -13213,17 +13213,17 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>8,910</t>
+          <t>13,530</t>
         </is>
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
-          <t>19,80</t>
+          <t>29,93</t>
         </is>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Fanta 33cl</t>
+          <t>Orangina 33cl</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
@@ -13260,17 +13260,17 @@
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>13,530</t>
+          <t>15,180</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>29,93</t>
+          <t>28,06</t>
         </is>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Orangina 33cl</t>
+          <t>[Page 11 - sirops Pêche/Grenadine/Citron + écart a fiabiliser]</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -13300,24 +13300,16 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D263" s="4" t="inlineStr">
-        <is>
-          <t>33,0</t>
-        </is>
-      </c>
+      <c r="D263" s="4" t="inlineStr"/>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F263" s="4" t="inlineStr">
-        <is>
-          <t>15,180</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr"/>
       <c r="G263" s="4" t="inlineStr">
         <is>
-          <t>28,06</t>
+          <t>94,59</t>
         </is>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -13327,7 +13319,7 @@
       </c>
       <c r="I263" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>pas de contenance au libelle</t>
         </is>
       </c>
     </row>
@@ -13339,7 +13331,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>[Page 11 - sirops Pêche/Grenadine/Citron + écart a fiabiliser]</t>
+          <t>Jus de Tomate 25cl</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -13347,26 +13339,34 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D264" s="4" t="inlineStr"/>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>25,0</t>
+        </is>
+      </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F264" s="4" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>4,750</t>
+        </is>
+      </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>94,59</t>
+          <t>19,38</t>
         </is>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
-          <t>a_verifier</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="I264" s="3" t="inlineStr">
         <is>
-          <t>pas de contenance au libelle</t>
+          <t>contenance lue au libelle</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Jus de Tomate 25cl</t>
+          <t>Jus Frais 25cl</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -13393,17 +13393,17 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>4,750</t>
+          <t>7,250</t>
         </is>
       </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
-          <t>19,38</t>
+          <t>35,38</t>
         </is>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Jus Frais 25cl</t>
+          <t>Perrier 33cl</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
@@ -13435,22 +13435,22 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>25,0</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
-          <t>7,250</t>
+          <t>12,870</t>
         </is>
       </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
-          <t>35,38</t>
+          <t>43,29</t>
         </is>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Perrier 33cl</t>
+          <t>San Pellegrino 100cl</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -13482,22 +13482,22 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>33,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>12,870</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
-          <t>43,29</t>
+          <t>33,32</t>
         </is>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>San Pellegrino 100cl</t>
+          <t>San Pellegrino 50cl</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
@@ -13529,22 +13529,22 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>50,0</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>33,32</t>
+          <t>43,20</t>
         </is>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>San Pellegrino 50cl</t>
+          <t>Vittel 100cl</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -13576,22 +13576,22 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>50,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
-          <t>43,20</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Vittel 100cl</t>
+          <t>Vittel 50cl</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
@@ -13623,22 +13623,22 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>100,0</t>
+          <t>50,0</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>10,32</t>
+          <t>9,80</t>
         </is>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Vittel 50cl</t>
+          <t>Limonade Mortuacienne 1L</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -13670,22 +13670,22 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>50,0</t>
+          <t>100,0</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>9,80</t>
+          <t>22,08</t>
         </is>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Limonade Mortuacienne 1L</t>
+          <t>Café grains 1kg</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
@@ -13715,24 +13715,16 @@
           <t>boisson_sans_alcool</t>
         </is>
       </c>
-      <c r="D272" s="4" t="inlineStr">
-        <is>
-          <t>100,0</t>
-        </is>
-      </c>
+      <c r="D272" s="4" t="inlineStr"/>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F272" s="4" t="inlineStr">
-        <is>
-          <t>23,000</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr"/>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>22,08</t>
+          <t>51,00</t>
         </is>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -13742,7 +13734,7 @@
       </c>
       <c r="I272" s="3" t="inlineStr">
         <is>
-          <t>contenance lue au libelle</t>
+          <t>pas de contenance au libelle</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13746,7 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Café grains 1kg</t>
+          <t>Café déca</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -13771,7 +13763,7 @@
       <c r="F273" s="4" t="inlineStr"/>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>51,00</t>
+          <t>19,56</t>
         </is>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -13780,45 +13772,6 @@
         </is>
       </c>
       <c r="I273" s="3" t="inlineStr">
-        <is>
-          <t>pas de contenance au libelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>Café déca</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>boisson_sans_alcool</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr"/>
-      <c r="E274" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F274" s="4" t="inlineStr"/>
-      <c r="G274" s="4" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
-      </c>
-      <c r="H274" s="4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="I274" s="3" t="inlineStr">
         <is>
           <t>pas de contenance au libelle</t>
         </is>
@@ -14007,7 +13960,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Notre transcription CSV retient un perimetre strictement « boissons » : elle exclut les biscuits, le sucre, les pailles et les consommables inscrits sur les memes pages. Elle porte en outre une colonne de fiabilite : 27 lignes sur 273 (1 929,34 EUR) y sont marquees « a verifier ». Les totaux en euros retenus ici sont ceux du document, non ceux du CSV.</t>
+          <t>Notre transcription CSV retient un perimetre strictement « boissons » : elle exclut les biscuits, le sucre, les pailles et les consommables inscrits sur les memes pages. Elle porte en outre une colonne de fiabilite : 27 lignes sur 272 (1 929,34 EUR) y sont marquees « a verifier ». Les totaux en euros retenus ici sont ceux du document, non ceux du CSV.</t>
         </is>
       </c>
     </row>
